--- a/outputs/53647.xlsx
+++ b/outputs/53647.xlsx
@@ -509,76 +509,80 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -586,19 +590,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="9" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="9" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -606,7 +610,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -614,11 +618,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="10" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="10" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -626,11 +630,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -642,7 +646,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -650,11 +654,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -662,11 +666,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -674,15 +678,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -690,11 +694,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="12" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="12" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -702,15 +706,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="12" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="12" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -718,15 +722,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="12" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="12" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -734,15 +738,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="14" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="14" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="144" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="144" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="13" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="13" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -750,7 +754,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="13" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="13" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -758,7 +762,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="13" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="13" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1014,354 +1018,354 @@
   <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="A1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="7" t="n">
+      <c r="A3" s="4"/>
+      <c r="B3" s="8" t="n">
         <v>44379</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="9"/>
+      <c r="E3" s="10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="10" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="9"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="E5" s="15"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="18" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20" t="n">
-        <f aca="false">IF(AND(D7&lt;&gt;"",C7=""),$E$32,IF(AND(C7&lt;&gt;"",D7=""),$E$31,""))</f>
+      <c r="D7" s="20"/>
+      <c r="E7" s="21" t="n">
+        <f aca="false">IF(C7&lt;&gt;"",E31,IF(D7&lt;&gt;"",E32,""))</f>
         <v>8.75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="18" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="19" t="n">
+      <c r="C8" s="22"/>
+      <c r="D8" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="20" t="n">
-        <f aca="false">IF(AND(D8&lt;&gt;"",C8=""),$E$32,IF(AND(C8&lt;&gt;"",D8=""),$E$31,""))</f>
+      <c r="E8" s="21" t="n">
+        <f aca="false">IF(C8&lt;&gt;"",E31,IF(D8&lt;&gt;"",E32,""))</f>
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20" t="str">
-        <f aca="false">IF(AND(D9&lt;&gt;"",C9=""),$E$32,IF(AND(C9&lt;&gt;"",D9=""),$E$31,""))</f>
+      <c r="A9" s="4"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="21" t="str">
+        <f aca="false">IF(C9&lt;&gt;"",E31,IF(D9&lt;&gt;"",E32,""))</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="20" t="str">
-        <f aca="false">IF(AND(D10&lt;&gt;"",C10=""),$E$32,IF(AND(C10&lt;&gt;"",D10=""),$E$31,""))</f>
+      <c r="A10" s="4"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21" t="str">
+        <f aca="false">IF(C10&lt;&gt;"",E31,IF(D10&lt;&gt;"",E32,""))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20" t="str">
-        <f aca="false">IF(AND(D11&lt;&gt;"",C11=""),$E$32,IF(AND(C11&lt;&gt;"",D11=""),$E$31,""))</f>
+      <c r="A11" s="23"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="21" t="str">
+        <f aca="false">IF(C11&lt;&gt;"",E31,IF(D11&lt;&gt;"",E32,""))</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="20" t="str">
-        <f aca="false">IF(AND(D12&lt;&gt;"",C12=""),$E$32,IF(AND(C12&lt;&gt;"",D12=""),$E$31,""))</f>
+      <c r="A12" s="23"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="21" t="str">
+        <f aca="false">IF(C12&lt;&gt;"",E31,IF(D12&lt;&gt;"",E32,""))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="20" t="str">
-        <f aca="false">IF(AND(D13&lt;&gt;"",C13=""),$E$32,IF(AND(C13&lt;&gt;"",D13=""),$E$31,""))</f>
+      <c r="A13" s="23"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21" t="str">
+        <f aca="false">IF(C13&lt;&gt;"",E31,IF(D13&lt;&gt;"",E32,""))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="20" t="str">
-        <f aca="false">IF(AND(D14&lt;&gt;"",C14=""),$E$32,IF(AND(C14&lt;&gt;"",D14=""),$E$31,""))</f>
+      <c r="A14" s="4"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21" t="str">
+        <f aca="false">IF(C14&lt;&gt;"",E31,IF(D14&lt;&gt;"",E32,""))</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20" t="str">
-        <f aca="false">IF(AND(D15&lt;&gt;"",C15=""),$E$32,IF(AND(C15&lt;&gt;"",D15=""),$E$31,""))</f>
+      <c r="A15" s="4"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="21" t="str">
+        <f aca="false">IF(C15&lt;&gt;"",E31,IF(D15&lt;&gt;"",E32,""))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="20" t="str">
-        <f aca="false">IF(AND(D16&lt;&gt;"",C16=""),$E$32,IF(AND(C16&lt;&gt;"",D16=""),$E$31,""))</f>
+      <c r="A16" s="4"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="21" t="str">
+        <f aca="false">IF(C16&lt;&gt;"",E31,IF(D16&lt;&gt;"",E32,""))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="4"/>
+      <c r="B17" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <f aca="false">SUM(C34,C5)</f>
         <v>70</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="27" t="n">
         <f aca="false">SUM(D34,D5)</f>
         <v>80</v>
       </c>
-      <c r="E17" s="27"/>
+      <c r="E17" s="28"/>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="28" t="s">
+      <c r="A18" s="4"/>
+      <c r="B18" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
-      <c r="B19" s="31" t="s">
+      <c r="A19" s="4"/>
+      <c r="B19" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="20" t="str">
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="21" t="str">
         <f aca="false">IF(C19&gt;1,E30,"")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="20" t="str">
+      <c r="A20" s="4"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21" t="str">
         <f aca="false">IF(C20&gt;1,E30,"")</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20" t="str">
+      <c r="A21" s="4"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="21" t="str">
         <f aca="false">IF(C21&gt;1,E30,"")</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="20"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="20" t="str">
+      <c r="A23" s="4"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="21" t="str">
         <f aca="false">IF(C23&gt;1,E30,"")</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3"/>
-      <c r="B24" s="37" t="s">
+      <c r="A24" s="4"/>
+      <c r="B24" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="20" t="str">
+      <c r="C24" s="39"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="21" t="str">
         <f aca="false">IF(C24&gt;1,E30,"")</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="43"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="44"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22"/>
-      <c r="B26" s="44" t="s">
+      <c r="A26" s="23"/>
+      <c r="B26" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="45" t="n">
+      <c r="C26" s="46" t="n">
         <f aca="false">SUM(C7:C11)</f>
         <v>8</v>
       </c>
-      <c r="D26" s="45"/>
-      <c r="E26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="47"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22"/>
-      <c r="B27" s="47" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="48" t="n">
+      <c r="C27" s="49" t="n">
         <f aca="false">SUM(D7:D16)</f>
         <v>8</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="51"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22"/>
-      <c r="B28" s="47" t="s">
+      <c r="A28" s="23"/>
+      <c r="B28" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="48" t="n">
+      <c r="C28" s="49" t="n">
         <f aca="false">SUM(C19:C24)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="51"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22"/>
-      <c r="B29" s="51" t="s">
+      <c r="A29" s="23"/>
+      <c r="B29" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="52" t="n">
+      <c r="C29" s="53" t="n">
         <f aca="false">SUM(C26:C28)</f>
         <v>16</v>
       </c>
-      <c r="D29" s="53"/>
-      <c r="E29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="55"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
-      <c r="B30" s="55" t="s">
+      <c r="A30" s="4"/>
+      <c r="B30" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="C30" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="57"/>
-      <c r="E30" s="58" t="n">
+      <c r="D30" s="58"/>
+      <c r="E30" s="59" t="n">
         <f aca="false">SUM(C17)/(C29)</f>
         <v>4.375</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3"/>
-      <c r="B31" s="59" t="s">
+      <c r="A31" s="4"/>
+      <c r="B31" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="60" t="n">
+      <c r="C31" s="57"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="61" t="n">
         <f aca="false">SUM(C5)/(C19+C20+C26+C21)</f>
         <v>8.75</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3"/>
-      <c r="B32" s="61" t="s">
+      <c r="A32" s="4"/>
+      <c r="B32" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="62" t="n">
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="63" t="n">
         <f aca="false">SUM(D5)/(C23+C24+C27)</f>
         <v>10</v>
       </c>
